--- a/tools/_out/groupB_20261021/stage/04_DESIGN_TABLES/DesignTable_6806.xlsx
+++ b/tools/_out/groupB_20261021/stage/04_DESIGN_TABLES/DesignTable_6806.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S29"/>
+  <dimension ref="A1:T29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -530,37 +530,42 @@
           <t>ORB_GRVW@DRIVE</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>$PRP@PartNo</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>$PRP@Threads</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>$PRP@DataStatus</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>$PRP@AxialSource</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>$COMMENT</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>$PRP@ScopeAction</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>$PRP@OMiSKU</t>
         </is>
@@ -605,32 +610,32 @@
       <c r="L3" s="3" t="n">
         <v>0.075</v>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>6806-04-02-NWO</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>7/16-20 (male ORB) x 1/8-27 (male NPTF)</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>ASSUMED</t>
-        </is>
-      </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
           <t>Air-Way s139 only (double-pass 17 rows); ORB end: measured/published groove set + MS51527 J2 thread length</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -675,33 +680,33 @@
       <c r="L4" s="3" t="n">
         <v>0.075</v>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>6806-04-04-NWO-FG</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>7/16-20 (male ORB) x 1/4-18 (male NPTF)</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>ASSUMED</t>
-        </is>
-      </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
           <t>Air-Way s139 only (double-pass 17 rows); ORB end: measured/published groove set + MS51527 J2 thread length</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
         <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>6806-04-04-NWO-FG</t>
         </is>
@@ -746,32 +751,32 @@
       <c r="L5" s="3" t="n">
         <v>0.075</v>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>6806-04-04-NWO</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>7/16-20 (male ORB) x 1/4-18 (male NPTF)</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>ASSUMED</t>
-        </is>
-      </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
           <t>Air-Way s139 only (double-pass 17 rows); ORB end: measured/published groove set + MS51527 J2 thread length</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -816,32 +821,32 @@
       <c r="L6" s="4" t="n">
         <v>0.075</v>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>6806-05-06-NWO</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>1/2-20 (male ORB) x 3/8-18 (male NPTF)</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>ASSUMED</t>
-        </is>
-      </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
           <t>Air-Way s139 only (double-pass 17 rows); ORB end: measured/published groove set + MS51527 J2 thread length</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="R6" s="4" t="inlineStr">
         <is>
           <t>C4 printed 1.63 both passes (a dash-5 ORB hex is ~0.63) - as-printed, likely decimal typo | DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -886,32 +891,32 @@
       <c r="L7" s="3" t="n">
         <v>0.083</v>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>6806-06-04-NWO</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>9/16-18 (male ORB) x 1/4-18 (male NPTF)</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>ASSUMED</t>
-        </is>
-      </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
           <t>Air-Way s139 only (double-pass 17 rows); ORB end: measured/published groove set + MS51527 J2 thread length</t>
         </is>
       </c>
-      <c r="Q7" s="3" t="inlineStr">
+      <c r="R7" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | near-match donor for OMi SKU 6806-06-04-NWO-FG</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -956,32 +961,32 @@
       <c r="L8" s="3" t="n">
         <v>0.083</v>
       </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>6806-06-06-NWO</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="O8" s="3" t="inlineStr">
         <is>
           <t>9/16-18 (male ORB) x 3/8-18 (male NPTF)</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>ASSUMED</t>
-        </is>
-      </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
           <t>Air-Way s139 only (double-pass 17 rows); ORB end: measured/published groove set + MS51527 J2 thread length</t>
         </is>
       </c>
-      <c r="Q8" s="3" t="inlineStr">
+      <c r="R8" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | near-match donor for OMi SKU 6806-06-06-NWO-FG</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1026,32 +1031,32 @@
       <c r="L9" s="3" t="n">
         <v>0.083</v>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>6806-06-08-NWO</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>9/16-18 (male ORB) x 1/2-14 (male NPTF)</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>ASSUMED</t>
-        </is>
-      </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
           <t>Air-Way s139 only (double-pass 17 rows); ORB end: measured/published groove set + MS51527 J2 thread length</t>
         </is>
       </c>
-      <c r="Q9" s="3" t="inlineStr">
+      <c r="R9" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1096,32 +1101,32 @@
       <c r="L10" s="3" t="n">
         <v>0.094</v>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>6806-08-08-NWO</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="O10" s="3" t="inlineStr">
         <is>
           <t>3/4-16 (male ORB) x 1/2-14 (male NPTF)</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>ASSUMED</t>
-        </is>
-      </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
           <t>Air-Way s139 only (double-pass 17 rows); ORB end: measured/published groove set + MS51527 J2 thread length</t>
         </is>
       </c>
-      <c r="Q10" s="3" t="inlineStr">
+      <c r="R10" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | near-match donor for OMi SKU 6806-08-08-NWO-FG</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1166,32 +1171,32 @@
       <c r="L11" s="3" t="n">
         <v>0.094</v>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="N11" s="3" t="inlineStr">
         <is>
           <t>6806-08-06-NWO</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>3/4-16 (male ORB) x 3/8-18 (male NPTF)</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>ASSUMED</t>
-        </is>
-      </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
           <t>Air-Way s139 only (double-pass 17 rows); ORB end: measured/published groove set + MS51527 J2 thread length</t>
         </is>
       </c>
-      <c r="Q11" s="3" t="inlineStr">
+      <c r="R11" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | near-match donor for OMi SKU 6806-08-06-NWO-FG</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1236,32 +1241,32 @@
       <c r="L12" s="3" t="n">
         <v>0.107</v>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="N12" s="3" t="inlineStr">
         <is>
           <t>6806-10-08-NWO</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>7/8-14 (male ORB) x 1/2-14 (male NPTF)</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>ASSUMED</t>
-        </is>
-      </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
           <t>Air-Way s139 only (double-pass 17 rows); ORB end: measured/published groove set + MS51527 J2 thread length</t>
         </is>
       </c>
-      <c r="Q12" s="3" t="inlineStr">
+      <c r="R12" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | near-match donor for OMi SKU 6806-10-08-NWO-FG</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1306,32 +1311,32 @@
       <c r="L13" s="3" t="n">
         <v>0.125</v>
       </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="N13" s="3" t="inlineStr">
         <is>
           <t>6806-12-12-NWO</t>
         </is>
       </c>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="O13" s="3" t="inlineStr">
         <is>
           <t>1 1/16-12 (male ORB) x 3/4-14 (male NPTF)</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>ASSUMED</t>
-        </is>
-      </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
           <t>Air-Way s139 only (double-pass 17 rows); ORB end: measured/published groove set + MS51527 J2 thread length</t>
         </is>
       </c>
-      <c r="Q13" s="3" t="inlineStr">
+      <c r="R13" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | near-match donor for OMi SKU 6806-12-12-NWO-FG</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1376,32 +1381,32 @@
       <c r="L14" s="3" t="n">
         <v>0.125</v>
       </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="N14" s="3" t="inlineStr">
         <is>
           <t>6806-12-16-NWO</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="O14" s="3" t="inlineStr">
         <is>
           <t>1 1/16-12 (male ORB) x 1-11 1/2 (male NPTF)</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>ASSUMED</t>
-        </is>
-      </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
           <t>Air-Way s139 only (double-pass 17 rows); ORB end: measured/published groove set + MS51527 J2 thread length</t>
         </is>
       </c>
-      <c r="Q14" s="3" t="inlineStr">
+      <c r="R14" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1446,32 +1451,32 @@
       <c r="L15" s="3" t="n">
         <v>0.125</v>
       </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="N15" s="3" t="inlineStr">
         <is>
           <t>6806-16-12-NWO</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
+      <c r="O15" s="3" t="inlineStr">
         <is>
           <t>1 5/16-12 (male ORB) x 3/4-14 (male NPTF)</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>ASSUMED</t>
-        </is>
-      </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
           <t>Air-Way s139 only (double-pass 17 rows); ORB end: measured/published groove set + MS51527 J2 thread length</t>
         </is>
       </c>
-      <c r="Q15" s="3" t="inlineStr">
+      <c r="R15" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1516,32 +1521,32 @@
       <c r="L16" s="3" t="n">
         <v>0.125</v>
       </c>
-      <c r="M16" s="3" t="inlineStr">
+      <c r="N16" s="3" t="inlineStr">
         <is>
           <t>6806-16-16-NWO</t>
         </is>
       </c>
-      <c r="N16" s="3" t="inlineStr">
+      <c r="O16" s="3" t="inlineStr">
         <is>
           <t>1 5/16-12 (male ORB) x 1-11 1/2 (male NPTF)</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>ASSUMED</t>
-        </is>
-      </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
           <t>Air-Way s139 only (double-pass 17 rows); ORB end: measured/published groove set + MS51527 J2 thread length</t>
         </is>
       </c>
-      <c r="Q16" s="3" t="inlineStr">
+      <c r="R16" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | near-match donor for OMi SKU 6806-16-16-NWO-FG</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1586,32 +1591,32 @@
       <c r="L17" s="3" t="n">
         <v>0.125</v>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="N17" s="3" t="inlineStr">
         <is>
           <t>6806-20-16-NWO</t>
         </is>
       </c>
-      <c r="N17" s="3" t="inlineStr">
+      <c r="O17" s="3" t="inlineStr">
         <is>
           <t>1 5/8-12 (male ORB) x 1-11 1/2 (male NPTF)</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>ASSUMED</t>
-        </is>
-      </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
           <t>Air-Way s139 only (double-pass 17 rows); ORB end: measured/published groove set + MS51527 J2 thread length</t>
         </is>
       </c>
-      <c r="Q17" s="3" t="inlineStr">
+      <c r="R17" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1656,32 +1661,32 @@
       <c r="L18" s="3" t="n">
         <v>0.125</v>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="N18" s="3" t="inlineStr">
         <is>
           <t>6806-20-20-NWO</t>
         </is>
       </c>
-      <c r="N18" s="3" t="inlineStr">
+      <c r="O18" s="3" t="inlineStr">
         <is>
           <t>1 5/8-12 (male ORB) x 1 1/4-11 1/2 (male NPTF)</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>ASSUMED</t>
-        </is>
-      </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
           <t>Air-Way s139 only (double-pass 17 rows); ORB end: measured/published groove set + MS51527 J2 thread length</t>
         </is>
       </c>
-      <c r="Q18" s="3" t="inlineStr">
+      <c r="R18" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | near-match donor for OMi SKU 6806-20-20-NWO-FG</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1726,32 +1731,32 @@
       <c r="L19" s="3" t="n">
         <v>0.125</v>
       </c>
-      <c r="M19" s="3" t="inlineStr">
+      <c r="N19" s="3" t="inlineStr">
         <is>
           <t>6806-24-24-NWO</t>
         </is>
       </c>
-      <c r="N19" s="3" t="inlineStr">
+      <c r="O19" s="3" t="inlineStr">
         <is>
           <t>1 7/8-12 (male ORB) x 1 1/2-11 1/2 (male NPTF)</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>ASSUMED</t>
-        </is>
-      </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
           <t>Air-Way s139 only (double-pass 17 rows); ORB end: measured/published groove set + MS51527 J2 thread length</t>
         </is>
       </c>
-      <c r="Q19" s="3" t="inlineStr">
+      <c r="R19" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | near-match donor for OMi SKU 6806-24-24-NWO-FG</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1763,32 +1768,61 @@
           <t>6806-06-04-NWO-FG</t>
         </is>
       </c>
+      <c r="B20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.54</v>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
           <t>6806-06-04-NWO-FG</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6806-06-04-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6806-06-04-NWO dims are NOT assumed; confirm before modelling</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: M7@DRIVE, N@DRIVE, C4HEX@HEX, Y@REF, D@BORE, D1@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6806-06-04-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6806-06-04-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6806-06-04-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: M7@DRIVE=M7, N@DRIVE=N, C4HEX@HEX=C, Y@REF=Y, D@BORE=BD, D1@BORE=AD; user 2026-10-21 "yes you can use them following my rule")</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>6806-06-04-NWO-FG</t>
         </is>
@@ -1800,32 +1834,61 @@
           <t>6806-06-06-NWO-FG</t>
         </is>
       </c>
+      <c r="B21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.675</v>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
           <t>6806-06-06-NWO-FG</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6806-06-06-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6806-06-06-NWO dims are NOT assumed; confirm before modelling</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: M7@DRIVE, N@DRIVE, C4HEX@HEX, Y@REF, D@BORE, D1@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6806-06-06-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6806-06-06-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6806-06-06-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: M7@DRIVE=M7, N@DRIVE=N, C4HEX@HEX=C, Y@REF=Y, D@BORE=BD, D1@BORE=AD; user 2026-10-21 "yes you can use them following my rule")</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>6806-06-06-NWO-FG</t>
         </is>
@@ -1837,32 +1900,61 @@
           <t>6806-08-06-NWO-FG</t>
         </is>
       </c>
+      <c r="B22" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.675</v>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
           <t>6806-08-06-NWO-FG</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6806-08-06-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6806-08-06-NWO dims are NOT assumed; confirm before modelling</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: M7@DRIVE, N@DRIVE, C4HEX@HEX, Y@REF, D@BORE, D1@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6806-08-06-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6806-08-06-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6806-08-06-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: M7@DRIVE=M7, N@DRIVE=N, C4HEX@HEX=C, Y@REF=Y, D@BORE=BD, D1@BORE=AD; user 2026-10-21 "yes you can use them following my rule")</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>6806-08-06-NWO-FG</t>
         </is>
@@ -1874,32 +1966,61 @@
           <t>6806-08-08-NWO-FG</t>
         </is>
       </c>
+      <c r="B23" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.84</v>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
           <t>6806-08-08-NWO-FG</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6806-08-08-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6806-08-08-NWO dims are NOT assumed; confirm before modelling</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: M7@DRIVE, N@DRIVE, C4HEX@HEX, Y@REF, D@BORE, D1@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6806-08-08-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6806-08-08-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6806-08-08-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: M7@DRIVE=M7, N@DRIVE=N, C4HEX@HEX=C, Y@REF=Y, D@BORE=BD, D1@BORE=AD; user 2026-10-21 "yes you can use them following my rule")</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>6806-08-08-NWO-FG</t>
         </is>
@@ -1911,32 +2032,61 @@
           <t>6806-10-08-NWO-FG</t>
         </is>
       </c>
+      <c r="B24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.84</v>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
           <t>6806-10-08-NWO-FG</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6806-10-08-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6806-10-08-NWO dims are NOT assumed; confirm before modelling</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: M7@DRIVE, N@DRIVE, C4HEX@HEX, Y@REF, D@BORE, D1@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6806-10-08-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6806-10-08-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6806-10-08-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: M7@DRIVE=M7, N@DRIVE=N, C4HEX@HEX=C, Y@REF=Y, D@BORE=BD, D1@BORE=AD; user 2026-10-21 "yes you can use them following my rule")</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>6806-10-08-NWO-FG</t>
         </is>
@@ -1948,32 +2098,38 @@
           <t>6806-12-08-NWO-FG</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="H25" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>6806-12-08-NWO-FG</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>6806-12-08-NWO-FG</t>
         </is>
@@ -1985,32 +2141,61 @@
           <t>6806-12-12-NWO-FG</t>
         </is>
       </c>
+      <c r="B26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.05</v>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
           <t>6806-12-12-NWO-FG</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6806-12-12-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6806-12-12-NWO dims are NOT assumed; confirm before modelling</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: M7@DRIVE, N@DRIVE, C4HEX@HEX, Y@REF, D@BORE, D1@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6806-12-12-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6806-12-12-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6806-12-12-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: M7@DRIVE=M7, N@DRIVE=N, C4HEX@HEX=C, Y@REF=Y, D@BORE=BD, D1@BORE=AD; user 2026-10-21 "yes you can use them following my rule")</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>6806-12-12-NWO-FG</t>
         </is>
@@ -2022,32 +2207,61 @@
           <t>6806-16-16-NWO-FG</t>
         </is>
       </c>
+      <c r="B27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.315</v>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
           <t>6806-16-16-NWO-FG</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6806-16-16-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6806-16-16-NWO dims are NOT assumed; confirm before modelling</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: M7@DRIVE, N@DRIVE, C4HEX@HEX, Y@REF, D@BORE, D1@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6806-16-16-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6806-16-16-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6806-16-16-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: M7@DRIVE=M7, N@DRIVE=N, C4HEX@HEX=C, Y@REF=Y, D@BORE=BD, D1@BORE=AD; user 2026-10-21 "yes you can use them following my rule")</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>6806-16-16-NWO-FG</t>
         </is>
@@ -2059,32 +2273,61 @@
           <t>6806-20-20-NWO-FG</t>
         </is>
       </c>
+      <c r="B28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.66</v>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
           <t>6806-20-20-NWO-FG</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6806-20-20-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6806-20-20-NWO dims are NOT assumed; confirm before modelling</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: M7@DRIVE, N@DRIVE, C4HEX@HEX, Y@REF, D@BORE, D1@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6806-20-20-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6806-20-20-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6806-20-20-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: M7@DRIVE=M7, N@DRIVE=N, C4HEX@HEX=C, Y@REF=Y, D@BORE=BD, D1@BORE=AD; user 2026-10-21 "yes you can use them following my rule")</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>6806-20-20-NWO-FG</t>
         </is>
@@ -2096,32 +2339,61 @@
           <t>6806-24-24-NWO-FG</t>
         </is>
       </c>
+      <c r="B29" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.9</v>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
           <t>6806-24-24-NWO-FG</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6806-24-24-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6806-24-24-NWO dims are NOT assumed; confirm before modelling</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: M7@DRIVE, N@DRIVE, C4HEX@HEX, Y@REF, D@BORE, D1@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6806-24-24-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6806-24-24-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6806-24-24-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: M7@DRIVE=M7, N@DRIVE=N, C4HEX@HEX=C, Y@REF=Y, D@BORE=BD, D1@BORE=AD; user 2026-10-21 "yes you can use them following my rule")</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>6806-24-24-NWO-FG</t>
         </is>
